--- a/sample_data/code_counts_20260420090000.xlsx
+++ b/sample_data/code_counts_20260420090000.xlsx
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3783</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="3">
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2223</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="4">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1814</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3409</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="6">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1920</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3854</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>931</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2283</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4406</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>581</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>320</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3411</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2421</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="15">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>187</v>
+        <v>538</v>
       </c>
     </row>
     <row r="16">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4384</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="17">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2294</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="18">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2090</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="19">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1047</v>
+        <v>2935</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/code_counts_20260420090000.xlsx
+++ b/sample_data/code_counts_20260420090000.xlsx
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1634</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3">
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4194</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3628</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2209</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="6">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1142</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4033</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2412</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4005</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4460</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4202</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>720</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="13">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>268</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="14">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2106</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="15">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>538</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1501</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="17">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3227</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3209</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="19">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2935</v>
+        <v>2524</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/code_counts_20260420090000.xlsx
+++ b/sample_data/code_counts_20260420090000.xlsx
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>509</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="3">
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>462</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="4">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2550</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3453</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="6">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3470</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3931</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2274</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3485</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3222</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2495</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3038</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="13">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1851</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="14">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2990</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="15">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207</v>
+        <v>787</v>
       </c>
     </row>
     <row r="16">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3370</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="17">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>425</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="18">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4393</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="19">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2524</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/code_counts_20260420090000.xlsx
+++ b/sample_data/code_counts_20260420090000.xlsx
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3566</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="3">
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4119</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="4">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>218</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2648</v>
+        <v>766</v>
       </c>
     </row>
     <row r="6">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3432</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3333</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2439</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3149</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1095</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>446</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2831</v>
+        <v>897</v>
       </c>
     </row>
     <row r="13">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1890</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="14">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2835</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="15">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="16">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2490</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="17">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1870</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="18">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2150</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>549</v>
+        <v>2270</v>
       </c>
     </row>
   </sheetData>
